--- a/htr-strucGenerale-CDA/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T10:35:11+00:00</t>
+    <t>2025-04-18T14:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-strucGenerale-CDA/ig/StructureDefinition-fr-core-custodian.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-fr-core-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T14:53:38+00:00</t>
+    <t>2025-04-22T14:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
